--- a/research/traditional_assets/database/data/sri_lanka/sri_lanka_insurance_general.xlsx
+++ b/research/traditional_assets/database/data/sri_lanka/sri_lanka_insurance_general.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AQ6"/>
+  <dimension ref="A1:AQ7"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -579,7 +579,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -588,46 +588,46 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.1148</v>
+        <v>0.165</v>
       </c>
       <c r="E2">
-        <v>0.178</v>
+        <v>0.2105</v>
       </c>
       <c r="G2">
-        <v>0.1890704584040747</v>
+        <v>0.2766497461928935</v>
       </c>
       <c r="H2">
-        <v>0.1890704584040747</v>
+        <v>0.2766497461928935</v>
       </c>
       <c r="I2">
-        <v>0.170606960950764</v>
+        <v>0.1857868020304569</v>
       </c>
       <c r="J2">
-        <v>0.1292921739888314</v>
+        <v>0.1512380245748787</v>
       </c>
       <c r="K2">
-        <v>61.931</v>
+        <v>54.27</v>
       </c>
       <c r="L2">
-        <v>0.1314325127334465</v>
+        <v>0.1620483726485518</v>
       </c>
       <c r="M2">
-        <v>12.409</v>
+        <v>8.536999999999999</v>
       </c>
       <c r="N2">
-        <v>0.02833751998173099</v>
+        <v>0.03150417004945014</v>
       </c>
       <c r="O2">
-        <v>0.2003681516526457</v>
+        <v>0.1573060622811866</v>
       </c>
       <c r="P2">
-        <v>12.409</v>
+        <v>8.536999999999999</v>
       </c>
       <c r="Q2">
-        <v>0.02833751998173099</v>
+        <v>0.03150417004945014</v>
       </c>
       <c r="R2">
-        <v>0.2003681516526457</v>
+        <v>0.1573060622811866</v>
       </c>
       <c r="S2">
         <v>0</v>
@@ -636,73 +636,73 @@
         <v>0</v>
       </c>
       <c r="U2">
-        <v>14.95</v>
+        <v>6.672</v>
       </c>
       <c r="V2">
-        <v>0.03414021466088148</v>
+        <v>0.02462174330208871</v>
       </c>
       <c r="W2">
-        <v>0.1312334020942852</v>
+        <v>0.1356542617046819</v>
       </c>
       <c r="X2">
-        <v>0.1151117951213022</v>
+        <v>0.2119280104603601</v>
       </c>
       <c r="Y2">
-        <v>0.01612160697298301</v>
+        <v>-0.07627374875567827</v>
       </c>
       <c r="Z2">
-        <v>1.140061600102586</v>
+        <v>0.7201995656007397</v>
       </c>
       <c r="AA2">
-        <v>0.1420893143434878</v>
+        <v>0.1079184303558837</v>
       </c>
       <c r="AB2">
-        <v>0.111585299760798</v>
+        <v>0.2076998854262319</v>
       </c>
       <c r="AC2">
-        <v>0.02913626375221595</v>
+        <v>-0.09858028676571209</v>
       </c>
       <c r="AD2">
-        <v>39.2</v>
+        <v>28.62</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>39.2</v>
+        <v>28.62</v>
       </c>
       <c r="AG2">
-        <v>24.25</v>
+        <v>21.948</v>
       </c>
       <c r="AH2">
-        <v>0.08216306853909033</v>
+        <v>0.09552736982643524</v>
       </c>
       <c r="AI2">
-        <v>0.08204269568857264</v>
+        <v>0.09552099325812696</v>
       </c>
       <c r="AJ2">
-        <v>0.05247214107973602</v>
+        <v>0.07492626174350012</v>
       </c>
       <c r="AK2">
-        <v>0.05239278383925679</v>
+        <v>0.07492114641506344</v>
       </c>
       <c r="AL2">
-        <v>2.594</v>
+        <v>2.704</v>
       </c>
       <c r="AM2">
-        <v>2.594</v>
+        <v>2.704</v>
       </c>
       <c r="AN2">
-        <v>0.452603625447408</v>
+        <v>0.4361475160012191</v>
       </c>
       <c r="AO2">
-        <v>30.99074787972244</v>
+        <v>23.0103550295858</v>
       </c>
       <c r="AP2">
-        <v>0.2799907631913174</v>
+        <v>0.3344711978055471</v>
       </c>
       <c r="AQ2">
-        <v>30.99074787972244</v>
+        <v>23.0103550295858</v>
       </c>
     </row>
     <row r="3">
@@ -713,7 +713,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Softlogic Life Insurance PLC (COSE:AAIC.N0000)</t>
+          <t>HNB Assurance PLC (COSE:HASU.N0000)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -722,46 +722,46 @@
         </is>
       </c>
       <c r="D3">
-        <v>0.292</v>
+        <v>0.167</v>
       </c>
       <c r="E3">
-        <v>0.155</v>
+        <v>0.226</v>
       </c>
       <c r="G3">
-        <v>0.1334681496461072</v>
+        <v>0.2010729613733905</v>
       </c>
       <c r="H3">
-        <v>0.1334681496461072</v>
+        <v>0.2010729613733905</v>
       </c>
       <c r="I3">
-        <v>0.1789686552072801</v>
+        <v>0.1800429184549356</v>
       </c>
       <c r="J3">
-        <v>0.125487378709666</v>
+        <v>0.1385798325545995</v>
       </c>
       <c r="K3">
-        <v>12</v>
+        <v>6.25</v>
       </c>
       <c r="L3">
-        <v>0.1213346814964611</v>
+        <v>0.1341201716738197</v>
       </c>
       <c r="M3">
-        <v>4.69</v>
+        <v>1.31</v>
       </c>
       <c r="N3">
-        <v>0.0357469512195122</v>
+        <v>0.07485714285714286</v>
       </c>
       <c r="O3">
-        <v>0.3908333333333334</v>
+        <v>0.2096</v>
       </c>
       <c r="P3">
-        <v>4.69</v>
+        <v>1.31</v>
       </c>
       <c r="Q3">
-        <v>0.0357469512195122</v>
+        <v>0.07485714285714286</v>
       </c>
       <c r="R3">
-        <v>0.3908333333333334</v>
+        <v>0.2096</v>
       </c>
       <c r="S3">
         <v>0</v>
@@ -770,73 +770,67 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>2.83</v>
+        <v>0</v>
       </c>
       <c r="V3">
-        <v>0.02157012195121951</v>
+        <v>0</v>
       </c>
       <c r="W3">
-        <v>0.2505219206680585</v>
+        <v>0.15625</v>
       </c>
       <c r="X3">
-        <v>0.1169172078250257</v>
+        <v>0.20174571385251</v>
       </c>
       <c r="Y3">
-        <v>0.1336047128430328</v>
+        <v>-0.04549571385250997</v>
       </c>
       <c r="Z3">
-        <v>2.089583773505177</v>
+        <v>1.445857896369842</v>
       </c>
       <c r="AA3">
-        <v>0.262216390331417</v>
+        <v>0.2003667451766781</v>
       </c>
       <c r="AB3">
-        <v>0.1125998140121886</v>
+        <v>0.20174571385251</v>
       </c>
       <c r="AC3">
-        <v>0.1496165763192284</v>
+        <v>-0.001378968675831899</v>
       </c>
       <c r="AD3">
-        <v>17.1</v>
+        <v>0</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>17.1</v>
+        <v>0</v>
       </c>
       <c r="AG3">
-        <v>14.27</v>
+        <v>0</v>
       </c>
       <c r="AH3">
-        <v>0.1153068105192178</v>
-      </c>
-      <c r="AI3">
-        <v>0.2537091988130564</v>
+        <v>0</v>
       </c>
       <c r="AJ3">
-        <v>0.09809582731834744</v>
-      </c>
-      <c r="AK3">
-        <v>0.221000464612049</v>
+        <v>0</v>
       </c>
       <c r="AL3">
-        <v>0.728</v>
+        <v>0.326</v>
       </c>
       <c r="AM3">
-        <v>0.728</v>
+        <v>0.326</v>
       </c>
       <c r="AN3">
-        <v>0.9243243243243244</v>
+        <v>0</v>
       </c>
       <c r="AO3">
-        <v>24.31318681318681</v>
+        <v>25.7361963190184</v>
       </c>
       <c r="AP3">
-        <v>0.7713513513513515</v>
+        <v>0</v>
       </c>
       <c r="AQ3">
-        <v>24.31318681318681</v>
+        <v>25.7361963190184</v>
       </c>
     </row>
     <row r="4">
@@ -856,43 +850,46 @@
         </is>
       </c>
       <c r="D4">
-        <v>0.05110000000000001</v>
+        <v>0.163</v>
+      </c>
+      <c r="E4">
+        <v>0.459</v>
       </c>
       <c r="G4">
-        <v>0.090625</v>
+        <v>0.1080459770114943</v>
       </c>
       <c r="H4">
-        <v>0.090625</v>
+        <v>0.1080459770114943</v>
       </c>
       <c r="I4">
-        <v>0.08385416666666667</v>
+        <v>0.1137931034482759</v>
       </c>
       <c r="J4">
-        <v>0.07239803403755869</v>
+        <v>0.1036017430845017</v>
       </c>
       <c r="K4">
-        <v>0.611</v>
+        <v>1.13</v>
       </c>
       <c r="L4">
-        <v>0.03182291666666667</v>
+        <v>0.06494252873563218</v>
       </c>
       <c r="M4">
-        <v>0.239</v>
+        <v>0.151</v>
       </c>
       <c r="N4">
-        <v>0.02115044247787611</v>
+        <v>0.02525083612040134</v>
       </c>
       <c r="O4">
-        <v>0.3911620294599018</v>
+        <v>0.1336283185840708</v>
       </c>
       <c r="P4">
-        <v>0.239</v>
+        <v>0.151</v>
       </c>
       <c r="Q4">
-        <v>0.02115044247787611</v>
+        <v>0.02525083612040134</v>
       </c>
       <c r="R4">
-        <v>0.3911620294599018</v>
+        <v>0.1336283185840708</v>
       </c>
       <c r="S4">
         <v>0</v>
@@ -901,73 +898,73 @@
         <v>0</v>
       </c>
       <c r="U4">
-        <v>1.12</v>
+        <v>0.678</v>
       </c>
       <c r="V4">
-        <v>0.09911504424778761</v>
+        <v>0.1133779264214047</v>
       </c>
       <c r="W4">
-        <v>0.07524630541871921</v>
+        <v>0.1356542617046819</v>
       </c>
       <c r="X4">
-        <v>0.1225074579009766</v>
+        <v>0.2375719721423561</v>
       </c>
       <c r="Y4">
-        <v>-0.04726115248225735</v>
+        <v>-0.1019177104376743</v>
       </c>
       <c r="Z4">
-        <v>2.08672970329312</v>
+        <v>1.816283924843424</v>
       </c>
       <c r="AA4">
-        <v>0.1510751280862001</v>
+        <v>0.1881701805501388</v>
       </c>
       <c r="AB4">
-        <v>0.1154481862795343</v>
+        <v>0.2186826094692114</v>
       </c>
       <c r="AC4">
-        <v>0.0356269418066658</v>
+        <v>-0.03051242891907258</v>
       </c>
       <c r="AD4">
-        <v>2.37</v>
+        <v>1.73</v>
       </c>
       <c r="AE4">
         <v>0</v>
       </c>
       <c r="AF4">
-        <v>2.37</v>
+        <v>1.73</v>
       </c>
       <c r="AG4">
-        <v>1.25</v>
+        <v>1.052</v>
       </c>
       <c r="AH4">
-        <v>0.1733723482077542</v>
+        <v>0.2243839169909209</v>
       </c>
       <c r="AI4">
-        <v>0.1684434968017058</v>
+        <v>0.1269258987527513</v>
       </c>
       <c r="AJ4">
-        <v>0.099601593625498</v>
+        <v>0.1496018202502844</v>
       </c>
       <c r="AK4">
-        <v>0.09652509652509653</v>
+        <v>0.08122297714638667</v>
       </c>
       <c r="AL4">
-        <v>0.2</v>
+        <v>0.181</v>
       </c>
       <c r="AM4">
-        <v>0.2</v>
+        <v>0.181</v>
       </c>
       <c r="AN4">
-        <v>1.445121951219512</v>
+        <v>0.865</v>
       </c>
       <c r="AO4">
-        <v>8.050000000000001</v>
+        <v>10.93922651933702</v>
       </c>
       <c r="AP4">
-        <v>0.7621951219512195</v>
+        <v>0.526</v>
       </c>
       <c r="AQ4">
-        <v>8.050000000000001</v>
+        <v>10.93922651933702</v>
       </c>
     </row>
     <row r="5">
@@ -987,46 +984,46 @@
         </is>
       </c>
       <c r="D5">
-        <v>0.08460000000000001</v>
+        <v>0.102</v>
       </c>
       <c r="E5">
-        <v>0.178</v>
+        <v>0.195</v>
       </c>
       <c r="G5">
-        <v>0.2243834664814172</v>
+        <v>0.309375</v>
       </c>
       <c r="H5">
-        <v>0.2243834664814172</v>
+        <v>0.309375</v>
       </c>
       <c r="I5">
-        <v>0.1837443556790552</v>
+        <v>0.2359375</v>
       </c>
       <c r="J5">
-        <v>0.1456510136480316</v>
+        <v>0.1882181736680328</v>
       </c>
       <c r="K5">
-        <v>44.2</v>
+        <v>37.5</v>
       </c>
       <c r="L5">
-        <v>0.1535255296978118</v>
+        <v>0.1953125</v>
       </c>
       <c r="M5">
-        <v>5.38</v>
+        <v>3.36</v>
       </c>
       <c r="N5">
-        <v>0.02072419106317411</v>
+        <v>0.02381289865343728</v>
       </c>
       <c r="O5">
-        <v>0.1217194570135746</v>
+        <v>0.0896</v>
       </c>
       <c r="P5">
-        <v>5.38</v>
+        <v>3.36</v>
       </c>
       <c r="Q5">
-        <v>0.02072419106317411</v>
+        <v>0.02381289865343728</v>
       </c>
       <c r="R5">
-        <v>0.1217194570135746</v>
+        <v>0.0896</v>
       </c>
       <c r="S5">
         <v>0</v>
@@ -1035,73 +1032,73 @@
         <v>0</v>
       </c>
       <c r="U5">
-        <v>6.53</v>
+        <v>2.79</v>
       </c>
       <c r="V5">
-        <v>0.02515408320493066</v>
+        <v>0.01977321048901488</v>
       </c>
       <c r="W5">
-        <v>0.1417120872074383</v>
+        <v>0.1152427781192379</v>
       </c>
       <c r="X5">
-        <v>0.1123241969502077</v>
+        <v>0.2097412556273451</v>
       </c>
       <c r="Y5">
-        <v>0.02938789025723058</v>
+        <v>-0.09449847750810723</v>
       </c>
       <c r="Z5">
-        <v>0.9138522092432707</v>
+        <v>0.5733688105284848</v>
       </c>
       <c r="AA5">
-        <v>0.1331035006007755</v>
+        <v>0.1079184303558837</v>
       </c>
       <c r="AB5">
-        <v>0.1104579149030094</v>
+        <v>0.2064987171215958</v>
       </c>
       <c r="AC5">
-        <v>0.0226455856977661</v>
+        <v>-0.09858028676571209</v>
       </c>
       <c r="AD5">
-        <v>16.9</v>
+        <v>9.109999999999999</v>
       </c>
       <c r="AE5">
         <v>0</v>
       </c>
       <c r="AF5">
-        <v>16.9</v>
+        <v>9.109999999999999</v>
       </c>
       <c r="AG5">
-        <v>10.37</v>
+        <v>6.319999999999999</v>
       </c>
       <c r="AH5">
-        <v>0.06112115732368897</v>
+        <v>0.06064842553758072</v>
       </c>
       <c r="AI5">
-        <v>0.04752530933633296</v>
+        <v>0.04057725713776669</v>
       </c>
       <c r="AJ5">
-        <v>0.03841167537133754</v>
+        <v>0.04287070953737621</v>
       </c>
       <c r="AK5">
-        <v>0.02970750852264588</v>
+        <v>0.02850441998917553</v>
       </c>
       <c r="AL5">
-        <v>1.05</v>
+        <v>0.632</v>
       </c>
       <c r="AM5">
-        <v>1.05</v>
+        <v>0.632</v>
       </c>
       <c r="AN5">
-        <v>0.2913793103448276</v>
+        <v>0.1917894736842105</v>
       </c>
       <c r="AO5">
-        <v>50.38095238095238</v>
+        <v>71.67721518987341</v>
       </c>
       <c r="AP5">
-        <v>0.1787931034482758</v>
+        <v>0.1330526315789474</v>
       </c>
       <c r="AQ5">
-        <v>50.38095238095238</v>
+        <v>71.67721518987341</v>
       </c>
     </row>
     <row r="6">
@@ -1112,7 +1109,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>HNB Assurance PLC (COSE:HASU.N0000)</t>
+          <t>Co-operative Insurance Company PLC (COSE:COOP.N0000)</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1120,47 +1117,41 @@
           <t>Insurance (General)</t>
         </is>
       </c>
-      <c r="D6">
-        <v>0.145</v>
-      </c>
-      <c r="E6">
-        <v>0.235</v>
-      </c>
       <c r="G6">
-        <v>0.1464723926380368</v>
+        <v>0.3430232558139535</v>
       </c>
       <c r="H6">
-        <v>0.1464723926380368</v>
+        <v>0.3430232558139535</v>
       </c>
       <c r="I6">
-        <v>0.1254601226993865</v>
+        <v>0.152906976744186</v>
       </c>
       <c r="J6">
-        <v>0.08457430084728683</v>
+        <v>0.1323542980886922</v>
       </c>
       <c r="K6">
-        <v>5.12</v>
+        <v>2.14</v>
       </c>
       <c r="L6">
-        <v>0.07852760736196319</v>
+        <v>0.1244186046511628</v>
       </c>
       <c r="M6">
-        <v>2.1</v>
+        <v>0.836</v>
       </c>
       <c r="N6">
-        <v>0.05865921787709498</v>
+        <v>0.04644444444444444</v>
       </c>
       <c r="O6">
-        <v>0.41015625</v>
+        <v>0.3906542056074766</v>
       </c>
       <c r="P6">
-        <v>2.1</v>
+        <v>0.836</v>
       </c>
       <c r="Q6">
-        <v>0.05865921787709498</v>
+        <v>0.04644444444444444</v>
       </c>
       <c r="R6">
-        <v>0.41015625</v>
+        <v>0.3906542056074766</v>
       </c>
       <c r="S6">
         <v>0</v>
@@ -1169,73 +1160,207 @@
         <v>0</v>
       </c>
       <c r="U6">
-        <v>4.47</v>
+        <v>0.534</v>
       </c>
       <c r="V6">
-        <v>0.1248603351955307</v>
+        <v>0.02966666666666667</v>
       </c>
       <c r="W6">
-        <v>0.1207547169811321</v>
+        <v>0.09907407407407408</v>
       </c>
       <c r="X6">
-        <v>0.1133063824175787</v>
+        <v>0.2119280104603601</v>
       </c>
       <c r="Y6">
-        <v>0.007448334563553399</v>
+        <v>-0.1128539363862861</v>
       </c>
       <c r="Z6">
-        <v>1.562050790608529</v>
+        <v>0.7236925148314889</v>
       </c>
       <c r="AA6">
-        <v>0.132109353503668</v>
+        <v>0.09578381483256219</v>
       </c>
       <c r="AB6">
-        <v>0.1105707855094074</v>
+        <v>0.2076998854262319</v>
       </c>
       <c r="AC6">
-        <v>0.02153856799426056</v>
+        <v>-0.1119160705936697</v>
       </c>
       <c r="AD6">
-        <v>2.83</v>
+        <v>1.48</v>
       </c>
       <c r="AE6">
         <v>0</v>
       </c>
       <c r="AF6">
-        <v>2.83</v>
+        <v>1.48</v>
       </c>
       <c r="AG6">
-        <v>-1.64</v>
+        <v>0.946</v>
       </c>
       <c r="AH6">
-        <v>0.07325912503235828</v>
+        <v>0.07597535934291581</v>
       </c>
       <c r="AI6">
-        <v>0.06948195433341518</v>
+        <v>0.08820023837902263</v>
       </c>
       <c r="AJ6">
-        <v>-0.04800936768149883</v>
+        <v>0.04993138393328406</v>
       </c>
       <c r="AK6">
-        <v>-0.04522890237175951</v>
+        <v>0.05822971808445155</v>
       </c>
       <c r="AL6">
-        <v>0.616</v>
+        <v>0.155</v>
       </c>
       <c r="AM6">
-        <v>0.616</v>
+        <v>0.155</v>
       </c>
       <c r="AN6">
-        <v>0.3341204250295159</v>
+        <v>0.4582043343653251</v>
       </c>
       <c r="AO6">
-        <v>13.27922077922078</v>
+        <v>16.96774193548387</v>
       </c>
       <c r="AP6">
-        <v>-0.1936245572609208</v>
+        <v>0.2928792569659442</v>
       </c>
       <c r="AQ6">
-        <v>13.27922077922078</v>
+        <v>16.96774193548387</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Sri Lanka</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Softlogic Life Insurance PLC (COSE:AAIC.N0000)</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Insurance (General)</t>
+        </is>
+      </c>
+      <c r="D7">
+        <v>0.266</v>
+      </c>
+      <c r="E7">
+        <v>0.173</v>
+      </c>
+      <c r="G7">
+        <v>0.2609400324149109</v>
+      </c>
+      <c r="H7">
+        <v>0.2609400324149109</v>
+      </c>
+      <c r="I7">
+        <v>0.06353322528363047</v>
+      </c>
+      <c r="J7">
+        <v>0.04617129284876448</v>
+      </c>
+      <c r="K7">
+        <v>7.25</v>
+      </c>
+      <c r="L7">
+        <v>0.1175040518638574</v>
+      </c>
+      <c r="M7">
+        <v>2.88</v>
+      </c>
+      <c r="N7">
+        <v>0.03257918552036199</v>
+      </c>
+      <c r="O7">
+        <v>0.3972413793103448</v>
+      </c>
+      <c r="P7">
+        <v>2.88</v>
+      </c>
+      <c r="Q7">
+        <v>0.03257918552036199</v>
+      </c>
+      <c r="R7">
+        <v>0.3972413793103448</v>
+      </c>
+      <c r="S7">
+        <v>0</v>
+      </c>
+      <c r="T7">
+        <v>0</v>
+      </c>
+      <c r="U7">
+        <v>2.67</v>
+      </c>
+      <c r="V7">
+        <v>0.03020361990950226</v>
+      </c>
+      <c r="W7">
+        <v>0.1441351888667992</v>
+      </c>
+      <c r="X7">
+        <v>0.2245802331195337</v>
+      </c>
+      <c r="Y7">
+        <v>-0.08044504425273444</v>
+      </c>
+      <c r="Z7">
+        <v>0.9555521139848226</v>
+      </c>
+      <c r="AA7">
+        <v>0.04411907648704923</v>
+      </c>
+      <c r="AB7">
+        <v>0.2139465474747928</v>
+      </c>
+      <c r="AC7">
+        <v>-0.1698274709877436</v>
+      </c>
+      <c r="AD7">
+        <v>16.3</v>
+      </c>
+      <c r="AE7">
+        <v>0</v>
+      </c>
+      <c r="AF7">
+        <v>16.3</v>
+      </c>
+      <c r="AG7">
+        <v>13.63</v>
+      </c>
+      <c r="AH7">
+        <v>0.1556829035339064</v>
+      </c>
+      <c r="AI7">
+        <v>0.3646532438478747</v>
+      </c>
+      <c r="AJ7">
+        <v>0.1335881603449966</v>
+      </c>
+      <c r="AK7">
+        <v>0.324292172257911</v>
+      </c>
+      <c r="AL7">
+        <v>1.41</v>
+      </c>
+      <c r="AM7">
+        <v>1.41</v>
+      </c>
+      <c r="AN7">
+        <v>3.7995337995338</v>
+      </c>
+      <c r="AO7">
+        <v>2.780141843971631</v>
+      </c>
+      <c r="AP7">
+        <v>3.177156177156177</v>
+      </c>
+      <c r="AQ7">
+        <v>2.780141843971631</v>
       </c>
     </row>
   </sheetData>

--- a/research/traditional_assets/database/data/sri_lanka/sri_lanka_insurance_general.xlsx
+++ b/research/traditional_assets/database/data/sri_lanka/sri_lanka_insurance_general.xlsx
@@ -588,46 +588,46 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.165</v>
+        <v>0.185</v>
       </c>
       <c r="E2">
-        <v>0.2105</v>
+        <v>-0.106</v>
       </c>
       <c r="G2">
-        <v>0.2766497461928935</v>
+        <v>0.1419665271966527</v>
       </c>
       <c r="H2">
-        <v>0.2766497461928935</v>
+        <v>0.1419665271966527</v>
       </c>
       <c r="I2">
-        <v>0.1857868020304569</v>
+        <v>0.1406882845188284</v>
       </c>
       <c r="J2">
-        <v>0.1512380245748787</v>
+        <v>0.1076018012048603</v>
       </c>
       <c r="K2">
-        <v>54.27</v>
+        <v>38.663</v>
       </c>
       <c r="L2">
-        <v>0.1620483726485518</v>
+        <v>0.08088493723849373</v>
       </c>
       <c r="M2">
-        <v>8.536999999999999</v>
+        <v>9.801</v>
       </c>
       <c r="N2">
-        <v>0.03150417004945014</v>
+        <v>0.03549029548088065</v>
       </c>
       <c r="O2">
-        <v>0.1573060622811866</v>
+        <v>0.2534981765512246</v>
       </c>
       <c r="P2">
-        <v>8.536999999999999</v>
+        <v>9.801</v>
       </c>
       <c r="Q2">
-        <v>0.03150417004945014</v>
+        <v>0.03549029548088065</v>
       </c>
       <c r="R2">
-        <v>0.1573060622811866</v>
+        <v>0.2534981765512246</v>
       </c>
       <c r="S2">
         <v>0</v>
@@ -636,73 +636,73 @@
         <v>0</v>
       </c>
       <c r="U2">
-        <v>6.672</v>
+        <v>26.971</v>
       </c>
       <c r="V2">
-        <v>0.02462174330208871</v>
+        <v>0.09766439745075318</v>
       </c>
       <c r="W2">
-        <v>0.1356542617046819</v>
+        <v>0.1354679802955665</v>
       </c>
       <c r="X2">
-        <v>0.2119280104603601</v>
+        <v>0.1947403665300052</v>
       </c>
       <c r="Y2">
-        <v>-0.07627374875567827</v>
+        <v>-0.05927238623443867</v>
       </c>
       <c r="Z2">
-        <v>0.7201995656007397</v>
+        <v>1.602994044105811</v>
       </c>
       <c r="AA2">
-        <v>0.1079184303558837</v>
+        <v>0.1245555494775997</v>
       </c>
       <c r="AB2">
-        <v>0.2076998854262319</v>
+        <v>0.1866978066271313</v>
       </c>
       <c r="AC2">
-        <v>-0.09858028676571209</v>
+        <v>-0.05727025101540978</v>
       </c>
       <c r="AD2">
-        <v>28.62</v>
+        <v>35.54</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>28.62</v>
+        <v>35.54</v>
       </c>
       <c r="AG2">
-        <v>21.948</v>
+        <v>8.568999999999999</v>
       </c>
       <c r="AH2">
-        <v>0.09552736982643524</v>
+        <v>0.1140198909207571</v>
       </c>
       <c r="AI2">
-        <v>0.09552099325812696</v>
+        <v>0.08785286992633608</v>
       </c>
       <c r="AJ2">
-        <v>0.07492626174350012</v>
+        <v>0.0300952835854444</v>
       </c>
       <c r="AK2">
-        <v>0.07492114641506344</v>
+        <v>0.02269518948854381</v>
       </c>
       <c r="AL2">
-        <v>2.704</v>
+        <v>4.431</v>
       </c>
       <c r="AM2">
-        <v>2.704</v>
+        <v>4.431</v>
       </c>
       <c r="AN2">
-        <v>0.4361475160012191</v>
+        <v>0.4961054189117507</v>
       </c>
       <c r="AO2">
-        <v>23.0103550295858</v>
+        <v>15.17693522906793</v>
       </c>
       <c r="AP2">
-        <v>0.3344711978055471</v>
+        <v>0.1196152879756554</v>
       </c>
       <c r="AQ2">
-        <v>23.0103550295858</v>
+        <v>15.17693522906793</v>
       </c>
     </row>
     <row r="3">
@@ -713,7 +713,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>HNB Assurance PLC (COSE:HASU.N0000)</t>
+          <t>Softlogic Life Insurance PLC (COSE:AAIC.N0000)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -722,46 +722,46 @@
         </is>
       </c>
       <c r="D3">
-        <v>0.167</v>
+        <v>0.25</v>
       </c>
       <c r="E3">
-        <v>0.226</v>
+        <v>-0.127</v>
       </c>
       <c r="G3">
-        <v>0.2010729613733905</v>
+        <v>0.06291390728476821</v>
       </c>
       <c r="H3">
-        <v>0.2010729613733905</v>
+        <v>0.06291390728476821</v>
       </c>
       <c r="I3">
-        <v>0.1800429184549356</v>
+        <v>0.1721854304635762</v>
       </c>
       <c r="J3">
-        <v>0.1385798325545995</v>
+        <v>0.1114752226535739</v>
       </c>
       <c r="K3">
-        <v>6.25</v>
+        <v>7.54</v>
       </c>
       <c r="L3">
-        <v>0.1341201716738197</v>
+        <v>0.08322295805739514</v>
       </c>
       <c r="M3">
-        <v>1.31</v>
+        <v>4.07</v>
       </c>
       <c r="N3">
-        <v>0.07485714285714286</v>
+        <v>0.06522435897435898</v>
       </c>
       <c r="O3">
-        <v>0.2096</v>
+        <v>0.5397877984084881</v>
       </c>
       <c r="P3">
-        <v>1.31</v>
+        <v>4.07</v>
       </c>
       <c r="Q3">
-        <v>0.07485714285714286</v>
+        <v>0.06522435897435898</v>
       </c>
       <c r="R3">
-        <v>0.2096</v>
+        <v>0.5397877984084881</v>
       </c>
       <c r="S3">
         <v>0</v>
@@ -770,67 +770,73 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="V3">
-        <v>0</v>
+        <v>0.05160256410256411</v>
       </c>
       <c r="W3">
-        <v>0.15625</v>
+        <v>0.2654929577464789</v>
       </c>
       <c r="X3">
-        <v>0.20174571385251</v>
+        <v>0.2057311747268672</v>
       </c>
       <c r="Y3">
-        <v>-0.04549571385250997</v>
+        <v>0.05976178301961171</v>
       </c>
       <c r="Z3">
-        <v>1.445857896369842</v>
+        <v>2.155603140613847</v>
       </c>
       <c r="AA3">
-        <v>0.2003667451766781</v>
+        <v>0.2402963400526717</v>
       </c>
       <c r="AB3">
-        <v>0.20174571385251</v>
+        <v>0.191471071212755</v>
       </c>
       <c r="AC3">
-        <v>-0.001378968675831899</v>
+        <v>0.04882526883991672</v>
       </c>
       <c r="AD3">
-        <v>0</v>
+        <v>17.3</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>0</v>
+        <v>17.3</v>
       </c>
       <c r="AG3">
-        <v>0</v>
+        <v>14.08</v>
       </c>
       <c r="AH3">
-        <v>0</v>
+        <v>0.2170639899623588</v>
+      </c>
+      <c r="AI3">
+        <v>0.3083778966131908</v>
       </c>
       <c r="AJ3">
-        <v>0</v>
+        <v>0.1841004184100418</v>
+      </c>
+      <c r="AK3">
+        <v>0.2662632375189108</v>
       </c>
       <c r="AL3">
-        <v>0.326</v>
+        <v>2.55</v>
       </c>
       <c r="AM3">
-        <v>0.326</v>
+        <v>2.55</v>
       </c>
       <c r="AN3">
-        <v>0</v>
+        <v>1.08125</v>
       </c>
       <c r="AO3">
-        <v>25.7361963190184</v>
+        <v>6.11764705882353</v>
       </c>
       <c r="AP3">
-        <v>0</v>
+        <v>0.88</v>
       </c>
       <c r="AQ3">
-        <v>25.7361963190184</v>
+        <v>6.11764705882353</v>
       </c>
     </row>
     <row r="4">
@@ -841,7 +847,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Amãna Takaful PLC (COSE:ATL.N0000)</t>
+          <t>Ceylinco Insurance PLC (COSE:CINS.N0000)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -850,46 +856,46 @@
         </is>
       </c>
       <c r="D4">
-        <v>0.163</v>
+        <v>0.133</v>
       </c>
       <c r="E4">
-        <v>0.459</v>
+        <v>-0.0679</v>
       </c>
       <c r="G4">
-        <v>0.1080459770114943</v>
+        <v>0.1905459875412239</v>
       </c>
       <c r="H4">
-        <v>0.1080459770114943</v>
+        <v>0.1905459875412239</v>
       </c>
       <c r="I4">
-        <v>0.1137931034482759</v>
+        <v>0.1762550384756321</v>
       </c>
       <c r="J4">
-        <v>0.1036017430845017</v>
+        <v>0.1321912788567241</v>
       </c>
       <c r="K4">
-        <v>1.13</v>
+        <v>28.6</v>
       </c>
       <c r="L4">
-        <v>0.06494252873563218</v>
+        <v>0.1048002931476732</v>
       </c>
       <c r="M4">
-        <v>0.151</v>
+        <v>3.68</v>
       </c>
       <c r="N4">
-        <v>0.02525083612040134</v>
+        <v>0.02193087008343266</v>
       </c>
       <c r="O4">
-        <v>0.1336283185840708</v>
+        <v>0.1286713286713287</v>
       </c>
       <c r="P4">
-        <v>0.151</v>
+        <v>3.68</v>
       </c>
       <c r="Q4">
-        <v>0.02525083612040134</v>
+        <v>0.02193087008343266</v>
       </c>
       <c r="R4">
-        <v>0.1336283185840708</v>
+        <v>0.1286713286713287</v>
       </c>
       <c r="S4">
         <v>0</v>
@@ -898,73 +904,73 @@
         <v>0</v>
       </c>
       <c r="U4">
-        <v>0.678</v>
+        <v>19.1</v>
       </c>
       <c r="V4">
-        <v>0.1133779264214047</v>
+        <v>0.1138259833134684</v>
       </c>
       <c r="W4">
-        <v>0.1356542617046819</v>
+        <v>0.1380975374215355</v>
       </c>
       <c r="X4">
-        <v>0.2375719721423561</v>
+        <v>0.1844228899751477</v>
       </c>
       <c r="Y4">
-        <v>-0.1019177104376743</v>
+        <v>-0.04632535255361223</v>
       </c>
       <c r="Z4">
-        <v>1.816283924843424</v>
+        <v>1.281677969604178</v>
       </c>
       <c r="AA4">
-        <v>0.1881701805501388</v>
+        <v>0.1694266498844658</v>
       </c>
       <c r="AB4">
-        <v>0.2186826094692114</v>
+        <v>0.1813685053620371</v>
       </c>
       <c r="AC4">
-        <v>-0.03051242891907258</v>
+        <v>-0.01194185547757121</v>
       </c>
       <c r="AD4">
-        <v>1.73</v>
+        <v>12.4</v>
       </c>
       <c r="AE4">
         <v>0</v>
       </c>
       <c r="AF4">
-        <v>1.73</v>
+        <v>12.4</v>
       </c>
       <c r="AG4">
-        <v>1.052</v>
+        <v>-6.700000000000001</v>
       </c>
       <c r="AH4">
-        <v>0.2243839169909209</v>
+        <v>0.0688124306326304</v>
       </c>
       <c r="AI4">
-        <v>0.1269258987527513</v>
+        <v>0.04389380530973452</v>
       </c>
       <c r="AJ4">
-        <v>0.1496018202502844</v>
+        <v>-0.04158907510862818</v>
       </c>
       <c r="AK4">
-        <v>0.08122297714638667</v>
+        <v>-0.02543659832953683</v>
       </c>
       <c r="AL4">
-        <v>0.181</v>
+        <v>1.01</v>
       </c>
       <c r="AM4">
-        <v>0.181</v>
+        <v>1.01</v>
       </c>
       <c r="AN4">
-        <v>0.865</v>
+        <v>0.2426614481409002</v>
       </c>
       <c r="AO4">
-        <v>10.93922651933702</v>
+        <v>47.62376237623762</v>
       </c>
       <c r="AP4">
-        <v>0.526</v>
+        <v>-0.1311154598825832</v>
       </c>
       <c r="AQ4">
-        <v>10.93922651933702</v>
+        <v>47.62376237623762</v>
       </c>
     </row>
     <row r="5">
@@ -975,7 +981,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Ceylinco Insurance PLC (COSE:CINS.N0000)</t>
+          <t>HNB Assurance PLC (COSE:HASU.N0000)</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -984,46 +990,46 @@
         </is>
       </c>
       <c r="D5">
-        <v>0.102</v>
+        <v>0.183</v>
       </c>
       <c r="E5">
-        <v>0.195</v>
+        <v>-0.106</v>
       </c>
       <c r="G5">
-        <v>0.309375</v>
+        <v>0.08983557548579969</v>
       </c>
       <c r="H5">
-        <v>0.309375</v>
+        <v>0.08983557548579969</v>
       </c>
       <c r="I5">
-        <v>0.2359375</v>
+        <v>0.04932735426008968</v>
       </c>
       <c r="J5">
-        <v>0.1882181736680328</v>
+        <v>0.03369888558362562</v>
       </c>
       <c r="K5">
-        <v>37.5</v>
+        <v>2.75</v>
       </c>
       <c r="L5">
-        <v>0.1953125</v>
+        <v>0.04110612855007473</v>
       </c>
       <c r="M5">
-        <v>3.36</v>
+        <v>1.7</v>
       </c>
       <c r="N5">
-        <v>0.02381289865343728</v>
+        <v>0.06463878326996197</v>
       </c>
       <c r="O5">
-        <v>0.0896</v>
+        <v>0.6181818181818182</v>
       </c>
       <c r="P5">
-        <v>3.36</v>
+        <v>1.7</v>
       </c>
       <c r="Q5">
-        <v>0.02381289865343728</v>
+        <v>0.06463878326996197</v>
       </c>
       <c r="R5">
-        <v>0.0896</v>
+        <v>0.6181818181818182</v>
       </c>
       <c r="S5">
         <v>0</v>
@@ -1032,73 +1038,73 @@
         <v>0</v>
       </c>
       <c r="U5">
-        <v>2.79</v>
+        <v>3.35</v>
       </c>
       <c r="V5">
-        <v>0.01977321048901488</v>
+        <v>0.1273764258555133</v>
       </c>
       <c r="W5">
-        <v>0.1152427781192379</v>
+        <v>0.1354679802955665</v>
       </c>
       <c r="X5">
-        <v>0.2097412556273451</v>
+        <v>0.1855245446829485</v>
       </c>
       <c r="Y5">
-        <v>-0.09449847750810723</v>
+        <v>-0.05005656438738204</v>
       </c>
       <c r="Z5">
-        <v>0.5733688105284848</v>
+        <v>3.696132596685083</v>
       </c>
       <c r="AA5">
-        <v>0.1079184303558837</v>
+        <v>0.1245555494775997</v>
       </c>
       <c r="AB5">
-        <v>0.2064987171215958</v>
+        <v>0.1818258004930094</v>
       </c>
       <c r="AC5">
-        <v>-0.09858028676571209</v>
+        <v>-0.05727025101540978</v>
       </c>
       <c r="AD5">
-        <v>9.109999999999999</v>
+        <v>2.22</v>
       </c>
       <c r="AE5">
         <v>0</v>
       </c>
       <c r="AF5">
-        <v>9.109999999999999</v>
+        <v>2.22</v>
       </c>
       <c r="AG5">
-        <v>6.319999999999999</v>
+        <v>-1.13</v>
       </c>
       <c r="AH5">
-        <v>0.06064842553758072</v>
+        <v>0.07784011220196355</v>
       </c>
       <c r="AI5">
-        <v>0.04057725713776669</v>
+        <v>0.07273918741808651</v>
       </c>
       <c r="AJ5">
-        <v>0.04287070953737621</v>
+        <v>-0.04489471593166467</v>
       </c>
       <c r="AK5">
-        <v>0.02850441998917553</v>
+        <v>-0.04158998895841001</v>
       </c>
       <c r="AL5">
-        <v>0.632</v>
+        <v>0.484</v>
       </c>
       <c r="AM5">
-        <v>0.632</v>
+        <v>0.484</v>
       </c>
       <c r="AN5">
-        <v>0.1917894736842105</v>
+        <v>0.6098901098901099</v>
       </c>
       <c r="AO5">
-        <v>71.67721518987341</v>
+        <v>6.818181818181818</v>
       </c>
       <c r="AP5">
-        <v>0.1330526315789474</v>
+        <v>-0.3104395604395604</v>
       </c>
       <c r="AQ5">
-        <v>71.67721518987341</v>
+        <v>6.818181818181818</v>
       </c>
     </row>
     <row r="6">
@@ -1109,7 +1115,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Co-operative Insurance Company PLC (COSE:COOP.N0000)</t>
+          <t>Amãna Takaful PLC (COSE:ATL.N0000)</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1117,41 +1123,44 @@
           <t>Insurance (General)</t>
         </is>
       </c>
+      <c r="D6">
+        <v>0.187</v>
+      </c>
       <c r="G6">
-        <v>0.3430232558139535</v>
+        <v>0.05511811023622047</v>
       </c>
       <c r="H6">
-        <v>0.3430232558139535</v>
+        <v>0.05511811023622047</v>
       </c>
       <c r="I6">
-        <v>0.152906976744186</v>
+        <v>0.01011811023622047</v>
       </c>
       <c r="J6">
-        <v>0.1323542980886922</v>
+        <v>0.007523207213412439</v>
       </c>
       <c r="K6">
-        <v>2.14</v>
+        <v>-0.029</v>
       </c>
       <c r="L6">
-        <v>0.1244186046511628</v>
+        <v>-0.001141732283464567</v>
       </c>
       <c r="M6">
-        <v>0.836</v>
+        <v>0.351</v>
       </c>
       <c r="N6">
-        <v>0.04644444444444444</v>
+        <v>0.04769021739130434</v>
       </c>
       <c r="O6">
-        <v>0.3906542056074766</v>
+        <v>-12.10344827586207</v>
       </c>
       <c r="P6">
-        <v>0.836</v>
+        <v>0.351</v>
       </c>
       <c r="Q6">
-        <v>0.04644444444444444</v>
+        <v>0.04769021739130434</v>
       </c>
       <c r="R6">
-        <v>0.3906542056074766</v>
+        <v>-12.10344827586207</v>
       </c>
       <c r="S6">
         <v>0</v>
@@ -1160,73 +1169,73 @@
         <v>0</v>
       </c>
       <c r="U6">
-        <v>0.534</v>
+        <v>0.757</v>
       </c>
       <c r="V6">
-        <v>0.02966666666666667</v>
+        <v>0.1028532608695652</v>
       </c>
       <c r="W6">
-        <v>0.09907407407407408</v>
+        <v>-0.003698979591836735</v>
       </c>
       <c r="X6">
-        <v>0.2119280104603601</v>
+        <v>0.1980356038025824</v>
       </c>
       <c r="Y6">
-        <v>-0.1128539363862861</v>
+        <v>-0.2017345833944191</v>
       </c>
       <c r="Z6">
-        <v>0.7236925148314889</v>
+        <v>2.856500224921278</v>
       </c>
       <c r="AA6">
-        <v>0.09578381483256219</v>
+        <v>0.02149004309724201</v>
       </c>
       <c r="AB6">
-        <v>0.2076998854262319</v>
+        <v>0.1871249865474843</v>
       </c>
       <c r="AC6">
-        <v>-0.1119160705936697</v>
+        <v>-0.1656349434502423</v>
       </c>
       <c r="AD6">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="AE6">
         <v>0</v>
       </c>
       <c r="AF6">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="AG6">
-        <v>0.946</v>
+        <v>0.743</v>
       </c>
       <c r="AH6">
-        <v>0.07597535934291581</v>
+        <v>0.1693002257336343</v>
       </c>
       <c r="AI6">
-        <v>0.08820023837902263</v>
+        <v>0.09615384615384616</v>
       </c>
       <c r="AJ6">
-        <v>0.04993138393328406</v>
+        <v>0.09169443416018759</v>
       </c>
       <c r="AK6">
-        <v>0.05822971808445155</v>
+        <v>0.05005726605133733</v>
       </c>
       <c r="AL6">
-        <v>0.155</v>
+        <v>0.211</v>
       </c>
       <c r="AM6">
-        <v>0.155</v>
+        <v>0.211</v>
       </c>
       <c r="AN6">
-        <v>0.4582043343653251</v>
+        <v>5.703422053231939</v>
       </c>
       <c r="AO6">
-        <v>16.96774193548387</v>
+        <v>1.218009478672986</v>
       </c>
       <c r="AP6">
-        <v>0.2928792569659442</v>
+        <v>2.825095057034221</v>
       </c>
       <c r="AQ6">
-        <v>16.96774193548387</v>
+        <v>1.218009478672986</v>
       </c>
     </row>
     <row r="7">
@@ -1237,7 +1246,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Softlogic Life Insurance PLC (COSE:AAIC.N0000)</t>
+          <t>Co-operative Insurance Company PLC (COSE:COOP.N0000)</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1245,122 +1254,113 @@
           <t>Insurance (General)</t>
         </is>
       </c>
-      <c r="D7">
-        <v>0.266</v>
-      </c>
-      <c r="E7">
-        <v>0.173</v>
-      </c>
       <c r="G7">
-        <v>0.2609400324149109</v>
+        <v>0.1238738738738739</v>
       </c>
       <c r="H7">
-        <v>0.2609400324149109</v>
+        <v>0.1238738738738739</v>
       </c>
       <c r="I7">
-        <v>0.06353322528363047</v>
+        <v>-0.0003603603603603604</v>
       </c>
       <c r="J7">
-        <v>0.04617129284876448</v>
+        <v>-0.0003603603603603604</v>
       </c>
       <c r="K7">
-        <v>7.25</v>
+        <v>-0.198</v>
       </c>
       <c r="L7">
-        <v>0.1175040518638574</v>
+        <v>-0.00891891891891892</v>
       </c>
       <c r="M7">
-        <v>2.88</v>
+        <v>-0</v>
       </c>
       <c r="N7">
-        <v>0.03257918552036199</v>
+        <v>-0</v>
       </c>
       <c r="O7">
-        <v>0.3972413793103448</v>
+        <v>0</v>
       </c>
       <c r="P7">
-        <v>2.88</v>
+        <v>-0</v>
       </c>
       <c r="Q7">
-        <v>0.03257918552036199</v>
+        <v>-0</v>
       </c>
       <c r="R7">
-        <v>0.3972413793103448</v>
+        <v>0</v>
       </c>
       <c r="S7">
         <v>0</v>
       </c>
-      <c r="T7">
-        <v>0</v>
-      </c>
       <c r="U7">
-        <v>2.67</v>
+        <v>0.544</v>
       </c>
       <c r="V7">
-        <v>0.03020361990950226</v>
+        <v>0.04422764227642276</v>
       </c>
       <c r="W7">
-        <v>0.1441351888667992</v>
+        <v>-0.01294117647058824</v>
       </c>
       <c r="X7">
-        <v>0.2245802331195337</v>
+        <v>0.1947403665300052</v>
       </c>
       <c r="Y7">
-        <v>-0.08044504425273444</v>
+        <v>-0.2076815430005934</v>
       </c>
       <c r="Z7">
-        <v>0.9555521139848226</v>
+        <v>1.366490212975501</v>
       </c>
       <c r="AA7">
-        <v>0.04411907648704923</v>
+        <v>-0.0004924289055767573</v>
       </c>
       <c r="AB7">
-        <v>0.2139465474747928</v>
+        <v>0.1866978066271313</v>
       </c>
       <c r="AC7">
-        <v>-0.1698274709877436</v>
+        <v>-0.187190235532708</v>
       </c>
       <c r="AD7">
-        <v>16.3</v>
+        <v>2.12</v>
       </c>
       <c r="AE7">
         <v>0</v>
       </c>
       <c r="AF7">
-        <v>16.3</v>
+        <v>2.12</v>
       </c>
       <c r="AG7">
-        <v>13.63</v>
+        <v>1.576</v>
       </c>
       <c r="AH7">
-        <v>0.1556829035339064</v>
+        <v>0.1470180305131761</v>
       </c>
       <c r="AI7">
-        <v>0.3646532438478747</v>
+        <v>0.106962663975782</v>
       </c>
       <c r="AJ7">
-        <v>0.1335881603449966</v>
+        <v>0.1135773998270395</v>
       </c>
       <c r="AK7">
-        <v>0.324292172257911</v>
+        <v>0.08175970118281801</v>
       </c>
       <c r="AL7">
-        <v>1.41</v>
+        <v>0.176</v>
       </c>
       <c r="AM7">
-        <v>1.41</v>
+        <v>0.176</v>
       </c>
       <c r="AN7">
-        <v>3.7995337995338</v>
+        <v>3.338582677165355</v>
       </c>
       <c r="AO7">
-        <v>2.780141843971631</v>
+        <v>-0.04545454545454546</v>
       </c>
       <c r="AP7">
-        <v>3.177156177156177</v>
+        <v>2.481889763779527</v>
       </c>
       <c r="AQ7">
-        <v>2.780141843971631</v>
+        <v>-0.04545454545454546</v>
       </c>
     </row>
   </sheetData>
